--- a/backtest_runs/20260410_193731/by_symbol/AKDSL/AKDSL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AKDSL/AKDSL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-5180.559999999997</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99663.59999999999</v>
@@ -679,7 +679,7 @@
         <v>-11740.36000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>87923.23999999999</v>
@@ -817,7 +817,7 @@
         <v>-2287.519999999999</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>94045.71999999999</v>
@@ -863,7 +863,7 @@
         <v>-3397.639999999994</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>90648.08</v>
@@ -909,7 +909,7 @@
         <v>-6257.04000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>84391.03999999999</v>
@@ -955,7 +955,7 @@
         <v>-1816.559999999997</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>82574.48</v>
@@ -1047,7 +1047,7 @@
         <v>-4575.039999999998</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>82204.44</v>
@@ -1185,7 +1185,7 @@
         <v>-5449.679999999991</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>89470.67999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-3094.880000000006</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>86375.79999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-7939.039999999998</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>78436.75999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-1244.679999999991</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>87956.88</v>
@@ -1461,7 +1461,7 @@
         <v>-3296.720000000002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>84660.16</v>
@@ -1645,7 +1645,7 @@
         <v>-3364</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>96535.08</v>
